--- a/Catalogo_Proyectos.xlsx
+++ b/Catalogo_Proyectos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="proyecto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="proyecto" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,16 +550,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -572,7 +571,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Azul oscuro = Obligatorio  |  Datos desde fila 4  |  LLAVE se forma: ID_DEPCIA-ID_UNIDAD-ID_PROGRAMA-CLAVE_PROYECTO</t>
+          <t xml:space="preserve">  Azul oscuro = Obligatorio  |  Datos desde fila 4  |  Repite la misma CLAVE_PROYECTO en varias filas para asignarle más de un programa/unidad</t>
         </is>
       </c>
     </row>
@@ -584,30 +583,25 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>EJERCICIO</t>
+          <t>ID_DEPCIA</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>ID_DEPCIA</t>
+          <t>ID_UNIDAD</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>ID_UNIDAD</t>
+          <t>ID_PROGRAMA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ID_PROGRAMA</t>
+          <t>CLAVE_PROYECTO</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CLAVE_PROYECTO</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>DESCRIPCION DEL PROYECTO</t>
         </is>
@@ -621,30 +615,25 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ej: 04</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Ej: 04</t>
+          <t>Ej: 04010101</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Ej: 04010101</t>
+          <t>Ej: E037</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Ej: E037</t>
+          <t>Ej: 04000127</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Ej: 04000127</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Ej: REMUNERACIONES AL PERSONAL ADMINISTRATIVO</t>
         </is>
@@ -656,30 +645,27 @@
           <t>04-04010101-E037-04000127</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>2025</v>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>04010101</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>04010101</t>
+          <t>E037</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>E037</t>
+          <t>04000127</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>04000127</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>REMUNERACIONES AL PERSONAL ADMINISTRATIVO Y DE APOYO DE LA SECRETARIA DE SEGURIDAD</t>
         </is>
@@ -691,30 +677,27 @@
           <t>04-04010101-E037-04000128</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>2025</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>04010101</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>04010101</t>
+          <t>E037</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>E037</t>
+          <t>04000128</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>04000128</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>REMUNERACIONES AL PERSONAL DE SEGURIDAD PUBLICA</t>
         </is>
@@ -726,30 +709,27 @@
           <t>07-07010101-E054-07000101</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>2025</v>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>07010101</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>07010101</t>
+          <t>E054</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>E054</t>
+          <t>07000101</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>07000101</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>REMUNERACIONES AL PERSONAL DOCENTE DE EDUCACION BASICA</t>
         </is>
@@ -761,30 +741,27 @@
           <t>08-08010101-F013-08000101</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>2025</v>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>08010101</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>08010101</t>
+          <t>F013</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>08000101</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>08000101</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>REMUNERACIONES AL PERSONAL MEDICO Y PARAMEDICO</t>
         </is>
@@ -796,30 +773,27 @@
           <t>21-21010101-M001-21000101</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>2025</v>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>21010101</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>21010101</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>21000101</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>21000101</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>REMUNERACIONES AL PERSONAL ADMINISTRATIVO DE OFICIALIA MAYOR</t>
         </is>
@@ -835,14 +809,13 @@
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
